--- a/assets/docs/lop3/Tieng Viet - Lop 3.xlsx
+++ b/assets/docs/lop3/Tieng Viet - Lop 3.xlsx
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Cóc kiện trời / Nói và nghe: Kể chuyện Cóc kiện trời</t>
+          <t>Cóc kiện Trời / Nói và nghe: Kể chuyện Cóc kiện trời</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>Ngọn lửa Ô- lim - Pich / Nói và nghe: Kể chuyện Đất quý, đất yêu</t>
+          <t>Ngọn lửa Ô-lim-pích / Nói và nghe: Kể chuyện Đất quý, đất yêu</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
